--- a/ladro_di_sabbia_bilanciamento.xlsx
+++ b/ladro_di_sabbia_bilanciamento.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="324">
   <si>
     <t xml:space="preserve">Il ladro di sabbia — Prototipo di bilanciamento economico (v3, ancorato a dati reali)</t>
   </si>
@@ -97,6 +97,9 @@
     <t xml:space="preserve">10) REGOLA FONDAMENTALE DEL MONDO: la sabbia non e' un oggetto fisico ne' un saldo impersonale in un caveau. Esiste solo dentro le persone e si trasferisce solo con il consenso del donatore (anche se estorto con minacce o tortura). Una banca non e' un forziere da scassinare: e' fatta di persone il cui compito e' accumulare sabbia per l'istituto e cederla su richiesta autorizzata - rapinarla significa coercere quelle persone specifiche. 'Sabbia sporca' e' solo un modo di dire per 'ottenuta illecitamente', non una sostanza diversa da ripulire su un mercato a parte. L'azione 'Vendere sabbia sporca a un compratore di alto livello' e' stata corretta per questo motivo (vedi colonna Fonte/nota).</t>
   </si>
   <si>
+    <t xml:space="preserve">11) COLONNA 'UNICA PER RUN' (aggiunta dopo un playtest automatico del prototipo Godot): 17 azioni su 60 rappresentano un bersaglio/accordo/evento singolo (es. IL GRANDE COLPO, la lotteria jackpot raro, il prestito esistenziale, un riscatto su una famiglia specifica) e sono marcate VERO - non ripetibili piu' volte nella stessa run. Senza questo vincolo il tetto economico calcolato dal prototipo saliva a centinaia di anni (fino a 643 col solo knapsack deterministico, ~399 medi con simulazione a dado vero), ben oltre il tetto di ~207 anni validato dalle simulazioni di questo foglio. Corretto in parallelo anche un bug scoperto nello stesso playtest: l'azione del portafoglio aveva costo 0h con guadagno positivo, quindi ripetibile all'infinito senza mai consumare il countdown - portata a 1h.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARAMETRI ECONOMICI (tarabili)</t>
   </si>
   <si>
@@ -130,6 +133,9 @@
     <t xml:space="preserve">Moralita'</t>
   </si>
   <si>
+    <t xml:space="preserve">Unica per run</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fonte / assunzione</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
     <t xml:space="preserve">Pulita</t>
   </si>
   <si>
+    <t xml:space="preserve">FALSO</t>
+  </si>
+  <si>
     <t xml:space="preserve">8h x 14,9€ mediano, netto -25% cuneo fiscale stimato</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
     <t xml:space="preserve">Ambigua</t>
   </si>
   <si>
+    <t xml:space="preserve">VERO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paga informale ~65% della mediana, non tassata (nessuna detrazione, ma nessuna tutela)</t>
   </si>
   <si>
@@ -307,7 +319,7 @@
     <t xml:space="preserve">Evento</t>
   </si>
   <si>
-    <t xml:space="preserve">Corretto da 'ritrovamento impersonale' (la sabbia non si trova per terra): il portafoglio e' solo un indizio per risalire al proprietario, che cede sotto pressione</t>
+    <t xml:space="preserve">Corretto da 'ritrovamento impersonale' (la sabbia non si trova per terra): il portafoglio e' solo un indizio per risalire al proprietario, che cede sotto pressione. Costo tempo corretto da 0h a 1h (trovato da un playtest automatico: a costo zero era ripetibile all'infinito senza mai consumare il countdown)</t>
   </si>
   <si>
     <t xml:space="preserve">Rintracci il proprietario di un portafoglio trovato e glielo restituisci</t>
@@ -565,7 +577,7 @@
     <t xml:space="preserve">Stima importo debito</t>
   </si>
   <si>
-    <t xml:space="preserve">Aggiungi altre righe qui sotto per nuove azioni (il Simulatore le trova automaticamente, range fino a riga 150). Cambia il salario mediano in B2 per ricalibrare TUTTA l'economia con un solo numero.</t>
+    <t xml:space="preserve">Aggiungi altre righe qui sotto per nuove azioni (il Simulatore le trova automaticamente, range fino a riga 150). Cambia il salario mediano in B2 per ricalibrare TUTTA l'economia con un solo numero. Colonna 'Unica per run' (VERO/FALSO): le azioni VERO rappresentano un bersaglio/accordo/evento singolo, non ripetibile piu' volte nella stessa run (trovato da un playtest automatico del prototipo: senza questo vincolo il tetto economico saliva molto oltre i 200 anni target).</t>
   </si>
   <si>
     <t xml:space="preserve">Simulatore di run — scegli una sequenza di azioni e guarda l'esito</t>
@@ -1079,7 +1091,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1102,6 +1114,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0CC"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1154,7 +1172,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1255,6 +1273,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1268,10 +1294,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1377,7 +1399,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFE0CC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1579,7 +1601,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C26"/>
+  <dimension ref="B2:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1699,6 +1721,11 @@
     <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1744,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1725,19 +1752,20 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>14.9</v>
@@ -1745,7 +1773,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="9" t="n">
         <v>8760</v>
@@ -1753,39 +1781,42 @@
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>8</v>
@@ -1805,18 +1836,21 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>16</v>
@@ -1836,18 +1870,21 @@
         <v>0.05</v>
       </c>
       <c r="H7" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>42</v>
+      <c r="J7" s="24" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>72</v>
@@ -1867,18 +1904,21 @@
         <v>0.2</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="19" t="n">
         <v>24</v>
@@ -1898,18 +1938,21 @@
         <v>0.15</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="24" t="s">
         <v>47</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>48</v>
@@ -1929,18 +1972,21 @@
         <v>0.05</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>2</v>
@@ -1960,18 +2006,21 @@
         <v>0</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>6</v>
@@ -1991,18 +2040,21 @@
         <v>0.35</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>8</v>
@@ -2022,18 +2074,21 @@
         <v>0.05</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>60</v>
+        <v>63</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5</v>
@@ -2053,18 +2108,21 @@
         <v>0.05</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>6</v>
@@ -2084,18 +2142,21 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>1</v>
@@ -2115,18 +2176,21 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C17" s="19" t="n">
         <v>4</v>
@@ -2146,18 +2210,21 @@
         <v>0.1</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>3</v>
@@ -2177,18 +2244,21 @@
         <v>0.05</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>72</v>
+        <v>47</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19" s="19" t="n">
         <v>0</v>
@@ -2208,18 +2278,21 @@
         <v>0</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>75</v>
+        <v>66</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>0</v>
@@ -2239,18 +2312,21 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C21" s="19" t="n">
         <v>2</v>
@@ -2270,18 +2346,21 @@
         <v>0.15</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>80</v>
+        <v>59</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>4</v>
@@ -2301,18 +2380,21 @@
         <v>0.05</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>82</v>
+        <v>47</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="C23" s="19" t="n">
         <v>2</v>
@@ -2332,18 +2414,21 @@
         <v>0.3</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>4</v>
@@ -2363,18 +2448,21 @@
         <v>0.1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>87</v>
+        <v>47</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C25" s="19" t="n">
         <v>2</v>
@@ -2394,18 +2482,21 @@
         <v>0</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>89</v>
+        <v>66</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>6</v>
@@ -2425,21 +2516,24 @@
         <v>0.15</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+      <c r="I26" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="20" t="n">
         <v>80</v>
@@ -2456,18 +2550,21 @@
         <v>0.15</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>94</v>
+        <v>59</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>2</v>
@@ -2487,18 +2584,21 @@
         <v>0</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>96</v>
+        <v>40</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>93</v>
       </c>
       <c r="C29" s="19" t="n">
         <v>3</v>
@@ -2518,18 +2618,21 @@
         <v>0.25</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>0</v>
@@ -2549,18 +2652,21 @@
         <v>1</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" s="19" t="n">
         <v>4</v>
@@ -2580,18 +2686,21 @@
         <v>0.3</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>102</v>
+        <v>59</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" s="24" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>4</v>
@@ -2611,18 +2720,21 @@
         <v>0.4</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" s="19" t="n">
         <v>3</v>
@@ -2642,18 +2754,21 @@
         <v>0</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>107</v>
+        <v>40</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" s="24" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>0</v>
@@ -2673,18 +2788,21 @@
         <v>1</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C35" s="19" t="n">
         <v>6</v>
@@ -2704,18 +2822,21 @@
         <v>0.1</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>2</v>
@@ -2735,18 +2856,21 @@
         <v>0.4</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>114</v>
+        <v>59</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C37" s="19" t="n">
         <v>1</v>
@@ -2766,18 +2890,21 @@
         <v>0.6</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>116</v>
+        <v>47</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>113</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>3</v>
@@ -2797,18 +2924,21 @@
         <v>0.45</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I38" s="17" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C39" s="19" t="n">
         <v>6</v>
@@ -2828,18 +2958,21 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>119</v>
+        <v>88</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C40" s="12" t="n">
         <v>8</v>
@@ -2859,18 +2992,21 @@
         <v>0.55</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I40" s="17" t="s">
-        <v>121</v>
+        <v>88</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C41" s="19" t="n">
         <v>1</v>
@@ -2890,18 +3026,21 @@
         <v>0.9</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>123</v>
+        <v>88</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>1</v>
@@ -2921,18 +3060,21 @@
         <v>0.2</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="17" t="s">
-        <v>126</v>
+        <v>59</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C43" s="19" t="n">
         <v>5</v>
@@ -2952,18 +3094,21 @@
         <v>0.35</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>128</v>
+        <v>59</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J43" s="24" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>4</v>
@@ -2983,18 +3128,21 @@
         <v>0.4</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>131</v>
+        <v>59</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C45" s="19" t="n">
         <v>12</v>
@@ -3014,18 +3162,21 @@
         <v>0.5</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="I45" s="24" t="s">
-        <v>133</v>
+        <v>88</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>72</v>
@@ -3045,18 +3196,21 @@
         <v>0.65</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I46" s="17" t="s">
-        <v>136</v>
+        <v>88</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C47" s="19" t="n">
         <v>2</v>
@@ -3076,18 +3230,21 @@
         <v>0.3</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>48</v>
@@ -3107,18 +3264,21 @@
         <v>0.6</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I48" s="17" t="s">
-        <v>140</v>
+        <v>88</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C49" s="19" t="n">
         <v>24</v>
@@ -3138,18 +3298,21 @@
         <v>0.45</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="I49" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J49" s="24" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>24</v>
@@ -3169,18 +3332,21 @@
         <v>0.55</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I50" s="17" t="s">
-        <v>146</v>
+        <v>88</v>
+      </c>
+      <c r="I50" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C51" s="19" t="n">
         <v>5</v>
@@ -3200,18 +3366,21 @@
         <v>0.35</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="I51" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C52" s="12" t="n">
         <v>1</v>
@@ -3231,18 +3400,21 @@
         <v>0.25</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I52" s="17" t="s">
-        <v>149</v>
+        <v>59</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C53" s="19" t="n">
         <v>3</v>
@@ -3262,18 +3434,21 @@
         <v>0.25</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="I53" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J53" s="24" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C54" s="12" t="n">
         <v>8</v>
@@ -3293,18 +3468,21 @@
         <v>0.5</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I54" s="17" t="s">
-        <v>153</v>
+        <v>88</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C55" s="19" t="n">
         <v>1</v>
@@ -3324,18 +3502,21 @@
         <v>0</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I55" s="24" t="s">
-        <v>157</v>
+        <v>160</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J55" s="24" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C56" s="12" t="n">
         <v>0</v>
@@ -3355,18 +3536,21 @@
         <v>0</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I56" s="17" t="s">
-        <v>159</v>
+        <v>66</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J56" s="17" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C57" s="19" t="n">
         <v>8</v>
@@ -3386,16 +3570,19 @@
         <v>0</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="I57" s="24"/>
+        <v>160</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>4</v>
@@ -3415,18 +3602,21 @@
         <v>0.15</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="I58" s="17" t="s">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="18" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C59" s="19" t="n">
         <v>0</v>
@@ -3446,18 +3636,21 @@
         <v>0</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>165</v>
+        <v>47</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J59" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C60" s="12" t="n">
         <v>2</v>
@@ -3477,18 +3670,21 @@
         <v>0.05</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I60" s="17" t="s">
-        <v>167</v>
+        <v>59</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J60" s="17" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C61" s="19" t="n">
         <v>6</v>
@@ -3508,18 +3704,21 @@
         <v>0.6</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="I61" s="24" t="s">
-        <v>170</v>
+        <v>88</v>
+      </c>
+      <c r="I61" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J61" s="24" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C62" s="12" t="n">
         <v>1</v>
@@ -3539,18 +3738,21 @@
         <v>0</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I62" s="17" t="s">
-        <v>70</v>
+        <v>40</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J62" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C63" s="19" t="n">
         <v>2</v>
@@ -3570,16 +3772,19 @@
         <v>0</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="I63" s="24"/>
+        <v>40</v>
+      </c>
+      <c r="I63" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J63" s="24"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C64" s="12" t="n">
         <v>4</v>
@@ -3599,18 +3804,21 @@
         <v>0.1</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="I64" s="17" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J64" s="17" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C65" s="19" t="n">
         <v>2</v>
@@ -3630,29 +3838,33 @@
         <v>0</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
+        <v>47</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J65" s="24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A67:J67"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3683,66 +3895,66 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="27" t="n">
+        <v>186</v>
+      </c>
+      <c r="B3" s="29" t="n">
         <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="27" t="n">
+        <v>187</v>
+      </c>
+      <c r="B4" s="29" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>36</v>
+      <c r="B7" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B7,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3777,8 +3989,8 @@
       <c r="A8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>154</v>
+      <c r="B8" s="25" t="s">
+        <v>158</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B8,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3813,8 +4025,8 @@
       <c r="A9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>160</v>
+      <c r="B9" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B9,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3849,8 +4061,8 @@
       <c r="A10" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>112</v>
+      <c r="B10" s="25" t="s">
+        <v>116</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B10,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3885,8 +4097,8 @@
       <c r="A11" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>66</v>
+      <c r="B11" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B11,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3921,8 +4133,8 @@
       <c r="A12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>124</v>
+      <c r="B12" s="25" t="s">
+        <v>128</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B12,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3957,8 +4169,8 @@
       <c r="A13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>175</v>
+      <c r="B13" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="C13" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B13,Azioni!$A$6:$A$150,0)),"")</f>
@@ -3993,8 +4205,8 @@
       <c r="A14" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>90</v>
+      <c r="B14" s="25" t="s">
+        <v>94</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B14,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4029,8 +4241,8 @@
       <c r="A15" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>154</v>
+      <c r="B15" s="30" t="s">
+        <v>158</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B15,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4065,8 +4277,8 @@
       <c r="A16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="29" t="s">
-        <v>73</v>
+      <c r="B16" s="25" t="s">
+        <v>77</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B16,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4101,8 +4313,8 @@
       <c r="A17" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>160</v>
+      <c r="B17" s="30" t="s">
+        <v>164</v>
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B17,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4137,8 +4349,8 @@
       <c r="A18" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>137</v>
+      <c r="B18" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B18,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4173,8 +4385,8 @@
       <c r="A19" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>78</v>
+      <c r="B19" s="30" t="s">
+        <v>82</v>
       </c>
       <c r="C19" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B19,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4209,8 +4421,8 @@
       <c r="A20" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="29" t="s">
-        <v>88</v>
+      <c r="B20" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="C20" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B20,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4245,8 +4457,8 @@
       <c r="A21" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="28" t="s">
-        <v>141</v>
+      <c r="B21" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="C21" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B21,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4281,8 +4493,8 @@
       <c r="A22" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="29" t="s">
-        <v>160</v>
+      <c r="B22" s="25" t="s">
+        <v>164</v>
       </c>
       <c r="C22" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B22,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4317,8 +4529,8 @@
       <c r="A23" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>134</v>
+      <c r="B23" s="30" t="s">
+        <v>138</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B23,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4353,8 +4565,8 @@
       <c r="A24" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="29" t="s">
-        <v>154</v>
+      <c r="B24" s="25" t="s">
+        <v>158</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B24,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4389,8 +4601,8 @@
       <c r="A25" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="28" t="s">
-        <v>173</v>
+      <c r="B25" s="30" t="s">
+        <v>177</v>
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">IFERROR(INDEX(Azioni!$C$6:$C$150,MATCH(B25,Azioni!$A$6:$A$150,0)),"")</f>
@@ -4423,50 +4635,50 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B28" s="30" t="n">
+        <v>198</v>
+      </c>
+      <c r="B28" s="31" t="n">
         <f aca="false">E25</f>
         <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B29" s="30" t="n">
+        <v>199</v>
+      </c>
+      <c r="B29" s="31" t="n">
         <f aca="false">F25</f>
         <v>201306.88590604</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B30" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="B30" s="31" t="n">
         <f aca="false">F25/8760</f>
         <v>22.9802381171279</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B31" s="27" t="n">
+        <v>201</v>
+      </c>
+      <c r="B31" s="29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B32" s="31" t="n">
+        <v>202</v>
+      </c>
+      <c r="B32" s="32" t="n">
         <f aca="false">B30-B31</f>
         <v>22.9802381171279</v>
       </c>
@@ -4501,816 +4713,816 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="A1" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
+      <c r="A2" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="s">
-        <v>201</v>
+      <c r="A4" s="35" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="E6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>211</v>
       </c>
+      <c r="B6" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>215</v>
+      <c r="C7" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>219</v>
+      <c r="A8" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="E9" s="36" t="s">
+      <c r="A9" s="37" t="s">
         <v>224</v>
       </c>
+      <c r="B9" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>229</v>
       </c>
+      <c r="B10" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
-        <v>230</v>
+      <c r="A13" s="35" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="C15" s="37" t="n">
+      <c r="A15" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="38" t="n">
         <v>6040.3</v>
       </c>
-      <c r="E15" s="38" t="n">
+      <c r="E15" s="39" t="n">
         <v>0.15</v>
       </c>
-      <c r="F15" s="36" t="s">
-        <v>236</v>
+      <c r="F15" s="37" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C16" s="39" t="n">
+      <c r="A16" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>93959.7</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="41" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="35" t="s">
-        <v>238</v>
+      <c r="F16" s="36" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="37" t="n">
+      <c r="A17" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="38" t="n">
         <v>8724.8</v>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E17" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="F17" s="36" t="s">
-        <v>241</v>
+      <c r="F17" s="37" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="C18" s="39" t="n">
+      <c r="A18" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>124161.1</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="41" t="n">
         <v>0.45</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>243</v>
+      <c r="F18" s="36" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="C19" s="37" t="n">
+      <c r="A19" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="38" t="n">
         <v>28</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="38" t="n">
         <v>17449.7</v>
       </c>
-      <c r="E19" s="38" t="n">
+      <c r="E19" s="39" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="36" t="s">
-        <v>246</v>
+      <c r="F19" s="37" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C20" s="39" t="n">
+      <c r="A20" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="C20" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="40" t="n">
         <v>140939.6</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="41" t="n">
         <v>0.35</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>248</v>
+      <c r="F20" s="36" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="C21" s="37" t="n">
+      <c r="A21" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="38" t="n">
         <v>17449.7</v>
       </c>
-      <c r="E21" s="38" t="n">
+      <c r="E21" s="39" t="n">
         <v>0.2</v>
       </c>
-      <c r="F21" s="36" t="s">
-        <v>250</v>
+      <c r="F21" s="37" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="39" t="n">
+      <c r="A22" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="40" t="n">
         <v>130872.5</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E22" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="F22" s="35" t="s">
-        <v>252</v>
+      <c r="F22" s="36" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="37" t="n">
+      <c r="A23" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="38" t="n">
         <v>28</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="38" t="n">
         <v>26174.5</v>
       </c>
-      <c r="E23" s="38" t="n">
+      <c r="E23" s="39" t="n">
         <v>0.15</v>
       </c>
-      <c r="F23" s="36" t="s">
-        <v>255</v>
+      <c r="F23" s="37" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="39" t="n">
+      <c r="A24" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="40" t="n">
         <v>36</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="40" t="n">
         <v>191275.2</v>
       </c>
-      <c r="E24" s="40" t="n">
+      <c r="E24" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>257</v>
+      <c r="F24" s="36" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="C25" s="37" t="n">
+      <c r="A25" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="38" t="n">
         <v>17449.7</v>
       </c>
-      <c r="E25" s="38" t="n">
+      <c r="E25" s="39" t="n">
         <v>0.1</v>
       </c>
-      <c r="F25" s="36" t="s">
-        <v>260</v>
+      <c r="F25" s="37" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="C26" s="39" t="n">
+      <c r="A26" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="40" t="n">
         <v>130872.5</v>
       </c>
-      <c r="E26" s="40" t="n">
+      <c r="E26" s="41" t="n">
         <v>0.25</v>
       </c>
-      <c r="F26" s="35" t="s">
-        <v>262</v>
+      <c r="F26" s="36" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="C27" s="37" t="n">
+      <c r="A27" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="C27" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="38" t="n">
         <v>17449.7</v>
       </c>
-      <c r="E27" s="38" t="n">
+      <c r="E27" s="39" t="n">
         <v>0.25</v>
       </c>
-      <c r="F27" s="36" t="s">
-        <v>265</v>
+      <c r="F27" s="37" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" s="39" t="n">
+      <c r="A28" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="40" t="n">
         <v>130872.5</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E28" s="41" t="n">
         <v>0.45</v>
       </c>
-      <c r="F28" s="35" t="s">
-        <v>267</v>
+      <c r="F28" s="36" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="A30" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="34" t="s">
-        <v>269</v>
+      <c r="A33" s="35" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
+      <c r="A34" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
+      <c r="A35" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
+      <c r="A36" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="B36" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34" t="s">
-        <v>276</v>
+      <c r="A39" s="35" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="B41" s="37" t="n">
+      <c r="A41" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="B41" s="38" t="n">
         <v>48</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="38" t="n">
         <v>124161.1</v>
       </c>
-      <c r="D41" s="38" t="n">
+      <c r="D41" s="39" t="n">
         <v>0.5</v>
       </c>
-      <c r="E41" s="36" t="s">
-        <v>279</v>
+      <c r="E41" s="37" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="B42" s="39" t="n">
+      <c r="A42" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B42" s="40" t="n">
         <v>40</v>
       </c>
-      <c r="C42" s="39" t="n">
+      <c r="C42" s="40" t="n">
         <v>157718.1</v>
       </c>
-      <c r="D42" s="40" t="n">
+      <c r="D42" s="41" t="n">
         <v>0.55</v>
       </c>
-      <c r="E42" s="35" t="s">
-        <v>281</v>
+      <c r="E42" s="36" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="B43" s="37" t="n">
+      <c r="A43" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="B43" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="C43" s="37" t="n">
+      <c r="C43" s="38" t="n">
         <v>87248.3</v>
       </c>
-      <c r="D43" s="38" t="n">
+      <c r="D43" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="E43" s="36" t="s">
-        <v>283</v>
+      <c r="E43" s="37" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="B44" s="39" t="n">
+      <c r="A44" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="C44" s="39" t="n">
+      <c r="C44" s="40" t="n">
         <v>177852.3</v>
       </c>
-      <c r="D44" s="40" t="n">
+      <c r="D44" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="E44" s="35" t="s">
-        <v>285</v>
+      <c r="E44" s="36" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="229.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="B45" s="37" t="n">
+      <c r="A45" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="B45" s="38" t="n">
         <v>72</v>
       </c>
-      <c r="C45" s="37" t="n">
+      <c r="C45" s="38" t="n">
         <v>265100.7</v>
       </c>
-      <c r="D45" s="38" t="n">
+      <c r="D45" s="39" t="n">
         <v>0.65</v>
       </c>
-      <c r="E45" s="36" t="s">
-        <v>287</v>
+      <c r="E45" s="37" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="B46" s="39" t="n">
+      <c r="A46" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="B46" s="40" t="n">
         <v>48</v>
       </c>
-      <c r="C46" s="39" t="n">
+      <c r="C46" s="40" t="n">
         <v>211409.4</v>
       </c>
-      <c r="D46" s="40" t="n">
+      <c r="D46" s="41" t="n">
         <v>0.55</v>
       </c>
-      <c r="E46" s="35" t="s">
-        <v>289</v>
+      <c r="E46" s="36" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="B47" s="37" t="n">
+      <c r="A47" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" s="38" t="n">
         <v>72</v>
       </c>
-      <c r="C47" s="37" t="n">
+      <c r="C47" s="38" t="n">
         <v>298657.7</v>
       </c>
-      <c r="D47" s="38" t="n">
+      <c r="D47" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="E47" s="36" t="s">
-        <v>291</v>
+      <c r="E47" s="37" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="B48" s="39" t="n">
+      <c r="A48" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" s="40" t="n">
         <v>48</v>
       </c>
-      <c r="C48" s="39" t="n">
+      <c r="C48" s="40" t="n">
         <v>104026.8</v>
       </c>
-      <c r="D48" s="40" t="n">
+      <c r="D48" s="41" t="n">
         <v>0.45</v>
       </c>
-      <c r="E48" s="35" t="s">
-        <v>293</v>
+      <c r="E48" s="36" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="B49" s="37" t="n">
+      <c r="A49" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="B49" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="C49" s="37" t="n">
+      <c r="C49" s="38" t="n">
         <v>191275.2</v>
       </c>
-      <c r="D49" s="38" t="n">
+      <c r="D49" s="39" t="n">
         <v>0.55</v>
       </c>
-      <c r="E49" s="36" t="s">
-        <v>295</v>
+      <c r="E49" s="37" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="B50" s="39" t="n">
+      <c r="A50" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" s="40" t="n">
         <v>48</v>
       </c>
-      <c r="C50" s="39" t="n">
+      <c r="C50" s="40" t="n">
         <v>157718.1</v>
       </c>
-      <c r="D50" s="40" t="n">
+      <c r="D50" s="41" t="n">
         <v>0.6</v>
       </c>
-      <c r="E50" s="35" t="s">
-        <v>297</v>
+      <c r="E50" s="36" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="34" t="s">
-        <v>298</v>
+      <c r="A53" s="35" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
+      <c r="A54" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="C57" s="36" t="s">
-        <v>305</v>
+      <c r="A57" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="B57" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="C57" s="37" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="36" t="s">
-        <v>306</v>
-      </c>
-      <c r="B58" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>308</v>
+      <c r="A58" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="B58" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="36" t="s">
-        <v>309</v>
-      </c>
-      <c r="B59" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="C59" s="36" t="s">
-        <v>311</v>
+      <c r="A59" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="37" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="34" t="s">
-        <v>312</v>
+      <c r="A62" s="35" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="B63" s="42"/>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
+      <c r="A63" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43"/>
+      <c r="F63" s="43"/>
     </row>
     <row r="64" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="B64" s="42"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
+      <c r="A64" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="43"/>
     </row>
     <row r="65" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="B65" s="42"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
+      <c r="A65" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="B65" s="43"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="43"/>
     </row>
     <row r="66" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B66" s="42"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
+      <c r="A66" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
     </row>
     <row r="67" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="42" t="s">
-        <v>317</v>
-      </c>
-      <c r="B67" s="42"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
+      <c r="A67" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
     </row>
     <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="B68" s="42"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
+      <c r="A68" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
     </row>
     <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="42" t="s">
-        <v>319</v>
-      </c>
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
+      <c r="A69" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="14">
